--- a/JP1/21_ドキュメント/JP1 Setupスクショ.xlsx
+++ b/JP1/21_ドキュメント/JP1 Setupスクショ.xlsx
@@ -5,34 +5,34 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tosa_git\proj-G-foot\JP1\21_ドキュメント\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tosa_git\proj_DHI_G-foot\JP1\21_ドキュメント\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7590826B-34A8-45F0-8406-2D32510339B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F17131-862D-480F-AA73-C85F375155EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{7860F748-19EC-4509-B706-54791C8E42AA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{7860F748-19EC-4509-B706-54791C8E42AA}"/>
   </bookViews>
   <sheets>
     <sheet name="setup スクショ" sheetId="1" r:id="rId1"/>
-    <sheet name="疎通確認エビデンス" sheetId="8" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
-    <sheet name="Cognos_Office_Connection_Cache" sheetId="11" state="veryHidden" r:id="rId4"/>
-    <sheet name="現行一覧" sheetId="9" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="4" r:id="rId7"/>
-    <sheet name="セットアップ後" sheetId="12" r:id="rId8"/>
-    <sheet name="エクスポートエビデンス" sheetId="6" r:id="rId9"/>
+    <sheet name="セットアップ後" sheetId="12" r:id="rId2"/>
+    <sheet name="疎通確認エビデンス" sheetId="8" r:id="rId3"/>
+    <sheet name="現行一覧（現行設定）" sheetId="9" r:id="rId4"/>
+    <sheet name="エクスポートエビデンス" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId6"/>
+    <sheet name="Cognos_Office_Connection_Cache" sheetId="11" state="veryHidden" r:id="rId7"/>
+    <sheet name="メモ１" sheetId="3" r:id="rId8"/>
+    <sheet name="メモ２" sheetId="4" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="ID" localSheetId="3" hidden="1">"5981d2c2-d314-4e05-b938-48a7fb0213a2"</definedName>
+    <definedName name="ID" localSheetId="6" hidden="1">"5981d2c2-d314-4e05-b938-48a7fb0213a2"</definedName>
     <definedName name="ID" localSheetId="0" hidden="1">"d92583c5-8ce3-4471-ab73-fc83fd86a04c"</definedName>
-    <definedName name="ID" localSheetId="2" hidden="1">"b3d16bb6-c49a-4bad-bb7d-c0ec0318a203"</definedName>
-    <definedName name="ID" localSheetId="5" hidden="1">"4be77172-9bd1-4d07-a2e9-38ee567ce778"</definedName>
-    <definedName name="ID" localSheetId="6" hidden="1">"8418e52f-4e59-4ec5-9053-d9f966925322"</definedName>
-    <definedName name="ID" localSheetId="8" hidden="1">"52c489aa-e2bf-4e54-a60f-b745f7d476a6"</definedName>
-    <definedName name="ID" localSheetId="7" hidden="1">"b80130ea-406b-4c99-9a6f-fa9ce28fa7b9"</definedName>
-    <definedName name="ID" localSheetId="4" hidden="1">"ddf47c5c-8433-4928-8e61-c44283253e90"</definedName>
-    <definedName name="ID" localSheetId="1" hidden="1">"7b25373b-6366-42e3-ac4a-dd8def093a3c"</definedName>
+    <definedName name="ID" localSheetId="5" hidden="1">"b3d16bb6-c49a-4bad-bb7d-c0ec0318a203"</definedName>
+    <definedName name="ID" localSheetId="4" hidden="1">"52c489aa-e2bf-4e54-a60f-b745f7d476a6"</definedName>
+    <definedName name="ID" localSheetId="1" hidden="1">"b80130ea-406b-4c99-9a6f-fa9ce28fa7b9"</definedName>
+    <definedName name="ID" localSheetId="7" hidden="1">"4be77172-9bd1-4d07-a2e9-38ee567ce778"</definedName>
+    <definedName name="ID" localSheetId="8" hidden="1">"8418e52f-4e59-4ec5-9053-d9f966925322"</definedName>
+    <definedName name="ID" localSheetId="3" hidden="1">"ddf47c5c-8433-4928-8e61-c44283253e90"</definedName>
+    <definedName name="ID" localSheetId="2" hidden="1">"7b25373b-6366-42e3-ac4a-dd8def093a3c"</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -2336,7 +2336,7 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2352,16 +2352,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2390,8 +2380,42 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="56" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="23" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
@@ -2402,25 +2426,10 @@
     <xf numFmtId="0" fontId="18" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="56" fontId="23" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="23" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2428,9 +2437,6 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2441,20 +2447,14 @@
     <xf numFmtId="0" fontId="27" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2549,23 +2549,6 @@
         <family val="3"/>
         <charset val="128"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <name val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </font>
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
@@ -2619,6 +2602,23 @@
         <family val="3"/>
         <charset val="128"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <name val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </font>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -12342,6 +12342,280 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>408409</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>113690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9617C54B-E6FB-32B1-6D33-F0820C7BE6EC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6172200" y="1428750"/>
+          <a:ext cx="9323809" cy="4876190"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>379838</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142262</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97DB73A2-B885-DC11-8596-A18EFDB0F3B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="476250"/>
+          <a:ext cx="9295238" cy="4904762"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>427457</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123214</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2814DDEE-B4DC-FE0A-1190-AC7EF174B133}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="5715000"/>
+          <a:ext cx="9342857" cy="4885714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>427457</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>94643</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E12A0EB-1A96-3C4A-737A-BBE12725548A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="10953750"/>
+          <a:ext cx="9342857" cy="4857143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>636895</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>218720</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC64E10-989C-2F3D-893A-929CF0D07D18}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1371600" y="15954375"/>
+          <a:ext cx="10238095" cy="2838095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>674562</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>27619</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A8AD040-9A1E-B3DC-4016-E302DD979C9E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="4048125"/>
+          <a:ext cx="13704762" cy="7647619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
@@ -13047,291 +13321,17 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>408409</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>113690</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9617C54B-E6FB-32B1-6D33-F0820C7BE6EC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6172200" y="1428750"/>
-          <a:ext cx="9323809" cy="4876190"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>379838</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>142262</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97DB73A2-B885-DC11-8596-A18EFDB0F3B2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1371600" y="476250"/>
-          <a:ext cx="9295238" cy="4904762"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>427457</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>123214</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2814DDEE-B4DC-FE0A-1190-AC7EF174B133}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1371600" y="5715000"/>
-          <a:ext cx="9342857" cy="4885714"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>427457</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>94643</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E12A0EB-1A96-3C4A-737A-BBE12725548A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1371600" y="10953750"/>
-          <a:ext cx="9342857" cy="4857143"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>636895</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>218720</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC64E10-989C-2F3D-893A-929CF0D07D18}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1371600" y="15954375"/>
-          <a:ext cx="10238095" cy="2838095"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>674562</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>27619</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A8AD040-9A1E-B3DC-4016-E302DD979C9E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="685800" y="4048125"/>
-          <a:ext cx="13704762" cy="7647619"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A19DF1C-1523-40CE-A980-5B23D474452B}" name="AgentList" displayName="AgentList" ref="B6:H21" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2A19DF1C-1523-40CE-A980-5B23D474452B}" name="AgentList" displayName="AgentList" ref="B6:H21" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="B6:H21" xr:uid="{2A19DF1C-1523-40CE-A980-5B23D474452B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C4610703-56D2-4497-ADBE-390110B8355F}" name="AGENT" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{B00E741E-28C2-4492-B9F2-31DBDF10DB46}" name="STATUS" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{C8A909CF-FE73-48D8-A0CE-A847BE0CE1EE}" name="HOST" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{F76EC053-F766-420B-9201-555930D4A385}" name="CON-EXE" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{7BA7D499-1C3A-46A8-825F-CA5B5E86CD10}" name="QUE" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{7D89C64B-6D31-4091-8473-1530D8B74EF6}" name="JOB" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{CE86E483-78BB-4FC7-B858-A8A9ECC0CFD5}" name="EVENT" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{C4610703-56D2-4497-ADBE-390110B8355F}" name="AGENT" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{B00E741E-28C2-4492-B9F2-31DBDF10DB46}" name="STATUS" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{C8A909CF-FE73-48D8-A0CE-A847BE0CE1EE}" name="HOST" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{F76EC053-F766-420B-9201-555930D4A385}" name="CON-EXE" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{7BA7D499-1C3A-46A8-825F-CA5B5E86CD10}" name="QUE" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{7D89C64B-6D31-4091-8473-1530D8B74EF6}" name="JOB" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{CE86E483-78BB-4FC7-B858-A8A9ECC0CFD5}" name="EVENT" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -13634,7 +13634,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="9">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -13657,7 +13657,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB0FD43-BF1C-45D4-B92B-5B9DB3909A17}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13666,3343 +13666,728 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34456845-7BEB-47A3-AFC6-90E43EAB56EA}">
-  <dimension ref="A1:B78"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" ht="26.1" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="9" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="9" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="9" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="9" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="9" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-    </row>
-    <row r="11" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="6" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-    </row>
-    <row r="14" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="1"/>
-      <c r="B14" s="4" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="1"/>
-      <c r="B15" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="1"/>
-      <c r="B16" s="6" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="1"/>
-      <c r="B17" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="1"/>
-      <c r="B19" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="1"/>
-      <c r="B22" s="4" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="1"/>
-      <c r="B23" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="1"/>
-      <c r="B24" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="1"/>
-      <c r="B25" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="1"/>
-      <c r="B26" s="6" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="1"/>
-      <c r="B27" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="1"/>
-      <c r="B30" s="4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="1"/>
-      <c r="B31" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="1"/>
-      <c r="B32" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="1"/>
-      <c r="B33" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="1"/>
-      <c r="B34" s="6" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="1"/>
-      <c r="B35" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="1"/>
-      <c r="B38" s="4" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="1"/>
-      <c r="B39" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="1"/>
-      <c r="B40" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="1"/>
-      <c r="B41" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="1"/>
-      <c r="B42" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="1"/>
-      <c r="B43" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="1"/>
-      <c r="B46" s="4" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="1"/>
-      <c r="B47" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="1"/>
-      <c r="B48" s="6" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="1"/>
-      <c r="B49" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="1"/>
-      <c r="B50" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="1"/>
-      <c r="B51" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-    </row>
-    <row r="54" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="1"/>
-      <c r="B54" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="1"/>
-      <c r="B55" s="5" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="1"/>
-      <c r="B56" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="1"/>
-      <c r="B57" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="57.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="1"/>
-      <c r="B58" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="1"/>
-      <c r="B59" s="8" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="1:2" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-    </row>
-    <row r="62" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-    </row>
-    <row r="63" spans="1:2" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="1"/>
-      <c r="B63" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="1"/>
-      <c r="B64" s="10" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="1"/>
-      <c r="B65" s="10" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="1"/>
-      <c r="B66" s="10" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="1"/>
-      <c r="B67" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="1"/>
-      <c r="B68" s="10"/>
-    </row>
-    <row r="69" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="1"/>
-      <c r="B69" s="10" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="1"/>
-      <c r="B70" s="10" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A71" s="1"/>
-      <c r="B71" s="10" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="1"/>
-      <c r="B72" s="10"/>
-    </row>
-    <row r="73" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="1"/>
-      <c r="B73" s="10" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="1"/>
-      <c r="B74" s="10" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A75" s="1"/>
-      <c r="B75" s="10"/>
-    </row>
-    <row r="76" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A76" s="1"/>
-      <c r="B76" s="10" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="1"/>
-      <c r="B77" s="10"/>
-    </row>
-    <row r="78" spans="1:2" ht="15.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="1"/>
-      <c r="B78" s="10" t="s">
-        <v>322</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB633387-CCD0-4B36-A8AF-1DE88DA1214B}">
-  <dimension ref="D86:D88"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D86" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.4">
-      <c r="D88" t="s">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF4739C-E82B-4160-8B82-56A8AC8BED06}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
-  <phoneticPr fontId="12"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <customProperties>
-    <customPr name="CafeStyleVersion" r:id="rId1"/>
-  </customProperties>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{764764F8-C3DF-4CCD-BFFC-91EDD895FCA3}">
-  <dimension ref="B1:H21"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
-    <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="13.625" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:8" ht="25.5" x14ac:dyDescent="0.5">
-      <c r="B1" s="11" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B3" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="C3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
-        <v>325</v>
-      </c>
-      <c r="C4" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B6" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="H6" s="13" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E7" s="13">
-        <v>5</v>
-      </c>
-      <c r="F7" s="13">
-        <v>0</v>
-      </c>
-      <c r="G7" s="13">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E8" s="13">
-        <v>8</v>
-      </c>
-      <c r="F8" s="13">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13">
-        <v>1</v>
-      </c>
-      <c r="H8" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B9" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="E9" s="13">
-        <v>5</v>
-      </c>
-      <c r="F9" s="13">
-        <v>0</v>
-      </c>
-      <c r="G9" s="13">
-        <v>1</v>
-      </c>
-      <c r="H9" s="13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B10" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E10" s="13">
-        <v>5</v>
-      </c>
-      <c r="F10" s="13">
-        <v>0</v>
-      </c>
-      <c r="G10" s="13">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B11" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E11" s="13">
-        <v>5</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B12" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="E12" s="13">
-        <v>5</v>
-      </c>
-      <c r="F12" s="13">
-        <v>0</v>
-      </c>
-      <c r="G12" s="13">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B13" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="E13" s="13">
-        <v>5</v>
-      </c>
-      <c r="F13" s="13">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B14" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E14" s="13">
-        <v>5</v>
-      </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B15" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E15" s="13">
-        <v>5</v>
-      </c>
-      <c r="F15" s="13">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B16" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="E16" s="13">
-        <v>5</v>
-      </c>
-      <c r="F16" s="13">
-        <v>0</v>
-      </c>
-      <c r="G16" s="13">
-        <v>0</v>
-      </c>
-      <c r="H16" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B17" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E17" s="13">
-        <v>5</v>
-      </c>
-      <c r="F17" s="13">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B18" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="E18" s="13">
-        <v>5</v>
-      </c>
-      <c r="F18" s="13">
-        <v>0</v>
-      </c>
-      <c r="G18" s="13">
-        <v>0</v>
-      </c>
-      <c r="H18" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B19" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E19" s="13">
-        <v>5</v>
-      </c>
-      <c r="F19" s="13">
-        <v>0</v>
-      </c>
-      <c r="G19" s="13">
-        <v>1</v>
-      </c>
-      <c r="H19" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B20" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E20" s="13">
-        <v>5</v>
-      </c>
-      <c r="F20" s="13">
-        <v>0</v>
-      </c>
-      <c r="G20" s="13">
-        <v>0</v>
-      </c>
-      <c r="H20" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B21" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="E21" s="13">
-        <v>5</v>
-      </c>
-      <c r="F21" s="13">
-        <v>0</v>
-      </c>
-      <c r="G21" s="13">
-        <v>1</v>
-      </c>
-      <c r="H21" s="13">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1291689E-9DDA-4BB4-AB16-F66FF3387759}">
-  <dimension ref="B2:B281"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B19" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B23" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B34" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B35" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B38" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B39" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B42" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B47" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B48" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B51" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B53" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B56" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B57" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B58" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B59" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B61" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B62" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B63" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B64" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B66" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B69" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B70" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B71" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B73" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B74" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B75" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B77" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B78" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B79" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B81" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B82" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B84" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B85" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B86" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B87" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B90" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B91" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B92" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="94" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B94" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B96" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B97" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="99" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B99" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B100" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B101" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B103" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="104" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B104" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="105" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B105" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B107" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B108" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="109" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B109" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B111" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B114" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B115" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B116" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B118" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B119" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="121" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B121" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B123" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B124" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B126" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="127" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B127" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="128" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B128" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B129" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B130" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="132" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B132" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B133" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B134" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B135" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="136" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B136" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B138" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B139" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B140" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B142" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B143" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B144" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B145" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B146" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B147" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B149" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B150" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B151" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B153" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B154" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B157" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B158" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B159" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B161" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B163" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B165" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B167" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B168" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B171" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B172" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B173" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B175" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B176" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B178" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B179" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B181" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B182" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B183" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="185" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B185" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B186" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B188" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B190" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B191" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B193" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B194" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B196" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B197" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B198" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="201" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B201" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B202" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B203" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B205" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B207" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B208" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B209" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B212" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="213" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B213" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B214" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B216" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B217" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B218" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B219" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B222" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B223" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B224" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B226" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B227" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B228" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B231" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B232" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B233" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B235" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B236" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B237" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B238" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B239" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B240" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="241" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B241" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="242" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B242" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="243" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B243" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="245" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B245" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="246" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B246" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="247" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B247" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="248" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B248" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="251" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B251" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="252" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B252" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="253" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B253" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="255" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B255" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B257" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B258" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="259" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B259" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B260" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B261" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="262" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B262" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B263" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B264" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="265" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B265" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B266" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B267" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B270" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B271" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="272" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B272" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B274" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="275" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B275" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B277" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="278" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B278" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="279" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B279" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="281" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B281" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70691334-4224-4996-88DA-06244D2EDD3B}">
-  <dimension ref="B2:B198"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B9" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B10" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B17" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B20" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B21" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B28" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B30" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B32" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B33" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B34" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B36" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B37" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B39" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B40" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B42" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B43" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B46" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B48" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B50" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B52" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B53" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B54" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B55" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B57" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B58" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B59" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B61" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B62" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B63" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B65" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B67" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B68" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B69" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B70" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B73" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B74" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B75" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B77" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B78" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B80" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B81" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B82" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B83" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B84" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B85" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B86" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="88" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B88" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="89" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B89" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="90" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B90" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="91" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B91" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="92" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B92" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="93" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B93" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="95" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B95" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="96" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B96" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="97" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B97" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="98" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B98" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="100" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B100" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="101" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B101" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="102" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B102" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="103" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B103" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B106" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B107" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B108" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B110" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="111" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B111" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="113" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B113" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="114" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B114" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="116" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B116" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="117" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B117" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="118" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B118" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="119" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B119" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="120" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B120" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="122" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B122" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="123" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B123" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="124" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B124" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="126" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B126" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="129" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B129" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="130" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B130" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="131" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B131" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B133" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="134" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B134" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="135" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B135" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="137" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B137" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="138" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B138" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="139" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B139" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="140" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B140" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="142" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B142" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="143" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B143" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="144" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B144" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B145" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B146" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B147" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B150" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B151" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B152" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B154" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B155" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B156" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B157" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B158" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B159" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B160" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B161" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B163" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B166" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B167" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B168" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B170" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B171" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B172" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B173" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B175" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B176" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B178" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B179" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B181" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="182" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B182" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="183" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B183" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="186" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B186" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="187" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B187" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="188" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B188" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="190" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B190" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="191" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B191" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B193" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B195" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B196" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B198" t="s">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41D78B3-EA6E-4243-A5A8-E999B75A4D65}">
   <dimension ref="B1:D222"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.375" customWidth="1"/>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="4" width="47.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="B1" s="14" t="s">
+    <row r="1" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+      <c r="B1" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-    </row>
-    <row r="2" spans="2:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="15" t="s">
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="2:4" ht="33.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="2:4" ht="18.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="15" t="s">
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+    </row>
+    <row r="3" spans="2:4" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="5" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="16" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+    </row>
+    <row r="4" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="5" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-    </row>
-    <row r="6" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="17" t="s">
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+    </row>
+    <row r="6" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-    </row>
-    <row r="7" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="20" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+    </row>
+    <row r="7" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="17" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="25" t="s">
+    <row r="8" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" s="21" t="s">
         <v>355</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>356</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="22" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="25" t="s">
+    <row r="9" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B9" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="22" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="23" t="s">
+    <row r="10" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="19" t="s">
         <v>361</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="20" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="16" t="s">
+    <row r="11" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="12" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-    </row>
-    <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="27" t="s">
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+    </row>
+    <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-    </row>
-    <row r="14" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="28" t="s">
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+    </row>
+    <row r="14" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-    </row>
-    <row r="15" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="31" t="s">
+      <c r="C14" s="37"/>
+      <c r="D14" s="38"/>
+    </row>
+    <row r="15" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-    </row>
-    <row r="16" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="27" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+    </row>
+    <row r="16" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="32" t="s">
         <v>367</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-    </row>
-    <row r="17" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="28" t="s">
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+    </row>
+    <row r="17" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="30"/>
-    </row>
-    <row r="18" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="31" t="s">
+      <c r="C17" s="37"/>
+      <c r="D17" s="38"/>
+    </row>
+    <row r="18" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B18" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-    </row>
-    <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="27" t="s">
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+    </row>
+    <row r="19" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="32" t="s">
         <v>370</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-    </row>
-    <row r="20" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="32" t="s">
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+    </row>
+    <row r="20" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B20" s="33" t="s">
         <v>371</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
-    </row>
-    <row r="21" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="28" t="s">
+      <c r="C20" s="34"/>
+      <c r="D20" s="35"/>
+    </row>
+    <row r="21" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B21" s="36" t="s">
         <v>372</v>
       </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-    </row>
-    <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="35" t="s">
+      <c r="C21" s="37"/>
+      <c r="D21" s="38"/>
+    </row>
+    <row r="22" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B22" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="35"/>
-      <c r="D22" s="35"/>
-    </row>
-    <row r="23" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B23" s="28" t="s">
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+    </row>
+    <row r="23" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B23" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="30"/>
-    </row>
-    <row r="24" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B24" s="31" t="s">
+      <c r="C23" s="37"/>
+      <c r="D23" s="38"/>
+    </row>
+    <row r="24" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B24" s="40" t="s">
         <v>374</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-    </row>
-    <row r="25" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B25" s="27" t="s">
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+    </row>
+    <row r="25" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B25" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-    </row>
-    <row r="26" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="20" t="s">
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+    </row>
+    <row r="26" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B26" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="41" t="s">
         <v>376</v>
       </c>
-      <c r="D26" s="39"/>
-    </row>
-    <row r="27" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B27" s="25" t="s">
+      <c r="D26" s="42"/>
+    </row>
+    <row r="27" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B27" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="D27" s="42"/>
-    </row>
-    <row r="28" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B28" s="25" t="s">
+      <c r="D27" s="44"/>
+    </row>
+    <row r="28" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B28" s="21" t="s">
         <v>361</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="D28" s="42"/>
-    </row>
-    <row r="29" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B29" s="25" t="s">
+      <c r="D28" s="44"/>
+    </row>
+    <row r="29" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B29" s="21" t="s">
         <v>378</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="D29" s="42"/>
-    </row>
-    <row r="30" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B30" s="25" t="s">
+      <c r="D29" s="44"/>
+    </row>
+    <row r="30" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B30" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="D30" s="42"/>
-    </row>
-    <row r="31" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="25" t="s">
+      <c r="D30" s="44"/>
+    </row>
+    <row r="31" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="21" t="s">
         <v>380</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="43" t="s">
         <v>377</v>
       </c>
-      <c r="D31" s="42"/>
-    </row>
-    <row r="32" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B32" s="25" t="s">
+      <c r="D31" s="44"/>
+    </row>
+    <row r="32" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="21" t="s">
         <v>381</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="43" t="s">
         <v>382</v>
       </c>
-      <c r="D32" s="42"/>
-    </row>
-    <row r="33" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="25" t="s">
+      <c r="D32" s="44"/>
+    </row>
+    <row r="33" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="43" t="s">
         <v>384</v>
       </c>
-      <c r="D33" s="42"/>
-    </row>
-    <row r="34" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B34" s="23" t="s">
+      <c r="D33" s="44"/>
+    </row>
+    <row r="34" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B34" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="43" t="s">
         <v>384</v>
       </c>
-      <c r="D34" s="42"/>
-    </row>
-    <row r="35" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="31" t="s">
+      <c r="D34" s="44"/>
+    </row>
+    <row r="35" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B35" s="40" t="s">
         <v>386</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
-    </row>
-    <row r="36" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B37" s="16" t="s">
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+    </row>
+    <row r="36" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="37" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-    </row>
-    <row r="38" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B38" s="27" t="s">
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+    </row>
+    <row r="38" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B38" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-    </row>
-    <row r="39" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B39" s="28" t="s">
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+    </row>
+    <row r="39" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B39" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="30"/>
-    </row>
-    <row r="40" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B40" s="31" t="s">
+      <c r="C39" s="37"/>
+      <c r="D39" s="38"/>
+    </row>
+    <row r="40" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B40" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="C40" s="31"/>
-      <c r="D40" s="31"/>
-    </row>
-    <row r="41" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="27" t="s">
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+    </row>
+    <row r="41" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B41" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-    </row>
-    <row r="42" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B42" s="17" t="s">
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+    </row>
+    <row r="42" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B42" s="31" t="s">
         <v>389</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-    </row>
-    <row r="43" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B43" s="27" t="s">
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+    </row>
+    <row r="43" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-    </row>
-    <row r="44" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B44" s="28" t="s">
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+    </row>
+    <row r="44" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="36" t="s">
         <v>390</v>
       </c>
-      <c r="C44" s="29"/>
-      <c r="D44" s="30"/>
-    </row>
-    <row r="45" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B45" s="35" t="s">
+      <c r="C44" s="37"/>
+      <c r="D44" s="38"/>
+    </row>
+    <row r="45" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B45" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-    </row>
-    <row r="46" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="17" t="s">
+      <c r="C45" s="39"/>
+      <c r="D45" s="39"/>
+    </row>
+    <row r="46" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="31" t="s">
         <v>391</v>
       </c>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-    </row>
-    <row r="47" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B48" s="16" t="s">
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+    </row>
+    <row r="47" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-    </row>
-    <row r="49" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B49" s="17" t="s">
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+    </row>
+    <row r="49" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B49" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-    </row>
-    <row r="50" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B50" s="27" t="s">
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+    </row>
+    <row r="50" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B50" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-    </row>
-    <row r="51" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="28" t="s">
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+    </row>
+    <row r="51" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B51" s="36" t="s">
         <v>392</v>
       </c>
-      <c r="C51" s="29"/>
-      <c r="D51" s="30"/>
-    </row>
-    <row r="52" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B52" s="35" t="s">
+      <c r="C51" s="37"/>
+      <c r="D51" s="38"/>
+    </row>
+    <row r="52" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B52" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="C52" s="35"/>
-      <c r="D52" s="35"/>
-    </row>
-    <row r="53" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B53" s="28" t="s">
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+    </row>
+    <row r="53" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B53" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="C53" s="29"/>
-      <c r="D53" s="30"/>
-    </row>
-    <row r="54" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B54" s="35" t="s">
+      <c r="C53" s="37"/>
+      <c r="D53" s="38"/>
+    </row>
+    <row r="54" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C54" s="35"/>
-      <c r="D54" s="35"/>
-    </row>
-    <row r="55" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B55" s="28" t="s">
+      <c r="C54" s="39"/>
+      <c r="D54" s="39"/>
+    </row>
+    <row r="55" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B55" s="36" t="s">
         <v>392</v>
       </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="30"/>
-    </row>
-    <row r="56" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="31" t="s">
+      <c r="C55" s="37"/>
+      <c r="D55" s="38"/>
+    </row>
+    <row r="56" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B56" s="40" t="s">
         <v>394</v>
       </c>
-      <c r="C56" s="31"/>
-      <c r="D56" s="31"/>
-    </row>
-    <row r="57" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B57" s="27" t="s">
+      <c r="C56" s="40"/>
+      <c r="D56" s="40"/>
+    </row>
+    <row r="57" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B57" s="32" t="s">
         <v>395</v>
       </c>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-    </row>
-    <row r="58" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B58" s="28" t="s">
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+    </row>
+    <row r="58" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B58" s="36" t="s">
         <v>396</v>
       </c>
-      <c r="C58" s="29"/>
-      <c r="D58" s="30"/>
-    </row>
-    <row r="59" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B59" s="31" t="s">
+      <c r="C58" s="37"/>
+      <c r="D58" s="38"/>
+    </row>
+    <row r="59" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B59" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C59" s="31"/>
-      <c r="D59" s="31"/>
-    </row>
-    <row r="60" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B61" s="16" t="s">
+      <c r="C59" s="40"/>
+      <c r="D59" s="40"/>
+    </row>
+    <row r="60" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="61" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B61" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-    </row>
-    <row r="62" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B62" s="27" t="s">
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+    </row>
+    <row r="62" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B62" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C62" s="27"/>
-      <c r="D62" s="27"/>
-    </row>
-    <row r="63" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B63" s="17" t="s">
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+    </row>
+    <row r="63" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B63" s="31" t="s">
         <v>397</v>
       </c>
-      <c r="C63" s="17"/>
-      <c r="D63" s="17"/>
-    </row>
-    <row r="64" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B64" s="27" t="s">
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+    </row>
+    <row r="64" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B64" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-    </row>
-    <row r="65" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B65" s="32" t="s">
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+    </row>
+    <row r="65" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B65" s="33" t="s">
         <v>398</v>
       </c>
-      <c r="C65" s="33"/>
-      <c r="D65" s="34"/>
-    </row>
-    <row r="66" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="20" t="s">
+      <c r="C65" s="34"/>
+      <c r="D65" s="35"/>
+    </row>
+    <row r="66" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B66" s="16" t="s">
         <v>399</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="D66" s="17" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="67" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B67" s="25" t="s">
+    <row r="67" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B67" s="21" t="s">
         <v>402</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="D67" s="26" t="s">
+      <c r="D67" s="22" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="68" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B68" s="37">
+    <row r="68" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B68" s="24">
         <v>46056</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="C68" s="15" t="s">
         <v>405</v>
       </c>
-      <c r="D68" s="26" t="s">
+      <c r="D68" s="22" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="69" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B69" s="36">
+    <row r="69" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B69" s="23">
         <v>46117</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C69" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="D69" s="24" t="s">
+      <c r="D69" s="20" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="70" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="35" t="s">
+    <row r="70" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B70" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-    </row>
-    <row r="71" spans="2:4" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B71" s="17" t="s">
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+    </row>
+    <row r="71" spans="2:4" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B71" s="31" t="s">
         <v>408</v>
       </c>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-    </row>
-    <row r="72" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B72" s="27" t="s">
+      <c r="C71" s="31"/>
+      <c r="D71" s="31"/>
+    </row>
+    <row r="72" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B72" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-    </row>
-    <row r="73" spans="2:4" ht="116.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B73" s="17" t="s">
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+    </row>
+    <row r="73" spans="2:4" ht="116.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B73" s="31" t="s">
         <v>409</v>
       </c>
-      <c r="C73" s="17"/>
-      <c r="D73" s="17"/>
-    </row>
-    <row r="74" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B74" s="27" t="s">
+      <c r="C73" s="31"/>
+      <c r="D73" s="31"/>
+    </row>
+    <row r="74" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B74" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-    </row>
-    <row r="75" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B75" s="28" t="s">
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+    </row>
+    <row r="75" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B75" s="36" t="s">
         <v>410</v>
       </c>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-    </row>
-    <row r="76" spans="2:4" ht="51.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="31" t="s">
+      <c r="C75" s="37"/>
+      <c r="D75" s="38"/>
+    </row>
+    <row r="76" spans="2:4" ht="51.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B76" s="40" t="s">
         <v>411</v>
       </c>
-      <c r="C76" s="31"/>
-      <c r="D76" s="31"/>
-    </row>
-    <row r="77" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="78" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B78" s="16" t="s">
+      <c r="C76" s="40"/>
+      <c r="D76" s="40"/>
+    </row>
+    <row r="77" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="78" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B78" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C78" s="16"/>
-      <c r="D78" s="16"/>
-    </row>
-    <row r="79" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B79" s="17" t="s">
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+    </row>
+    <row r="79" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B79" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-    </row>
-    <row r="80" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B80" s="28" t="s">
+      <c r="C79" s="31"/>
+      <c r="D79" s="31"/>
+    </row>
+    <row r="80" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B80" s="36" t="s">
         <v>412</v>
       </c>
-      <c r="C80" s="29"/>
-      <c r="D80" s="30"/>
-    </row>
-    <row r="81" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B81" s="31" t="s">
+      <c r="C80" s="37"/>
+      <c r="D80" s="38"/>
+    </row>
+    <row r="81" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B81" s="40" t="s">
         <v>413</v>
       </c>
-      <c r="C81" s="31"/>
-      <c r="D81" s="31"/>
-    </row>
-    <row r="82" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="83" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B83" s="16" t="s">
+      <c r="C81" s="40"/>
+      <c r="D81" s="40"/>
+    </row>
+    <row r="82" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="83" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B83" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-    </row>
-    <row r="84" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B84" s="27" t="s">
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+    </row>
+    <row r="84" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B84" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
-    </row>
-    <row r="85" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B85" s="28" t="s">
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+    </row>
+    <row r="85" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B85" s="36" t="s">
         <v>414</v>
       </c>
-      <c r="C85" s="29"/>
-      <c r="D85" s="30"/>
-    </row>
-    <row r="86" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="31" t="s">
+      <c r="C85" s="37"/>
+      <c r="D85" s="38"/>
+    </row>
+    <row r="86" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B86" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="C86" s="31"/>
-      <c r="D86" s="31"/>
-    </row>
-    <row r="87" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B87" s="27" t="s">
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+    </row>
+    <row r="87" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B87" s="32" t="s">
         <v>416</v>
       </c>
-      <c r="C87" s="27"/>
-      <c r="D87" s="27"/>
-    </row>
-    <row r="88" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B88" s="28" t="s">
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+    </row>
+    <row r="88" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B88" s="36" t="s">
         <v>417</v>
       </c>
-      <c r="C88" s="29"/>
-      <c r="D88" s="30"/>
-    </row>
-    <row r="89" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B89" s="31" t="s">
+      <c r="C88" s="37"/>
+      <c r="D88" s="38"/>
+    </row>
+    <row r="89" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B89" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="C89" s="31"/>
-      <c r="D89" s="31"/>
-    </row>
-    <row r="90" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B90" s="27" t="s">
+      <c r="C89" s="40"/>
+      <c r="D89" s="40"/>
+    </row>
+    <row r="90" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B90" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-    </row>
-    <row r="91" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B91" s="28" t="s">
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+    </row>
+    <row r="91" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B91" s="36" t="s">
         <v>419</v>
       </c>
-      <c r="C91" s="29"/>
-      <c r="D91" s="30"/>
-    </row>
-    <row r="92" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B92" s="35" t="s">
+      <c r="C91" s="37"/>
+      <c r="D91" s="38"/>
+    </row>
+    <row r="92" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B92" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="C92" s="35"/>
-      <c r="D92" s="35"/>
-    </row>
-    <row r="93" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B93" s="28" t="s">
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+    </row>
+    <row r="93" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B93" s="36" t="s">
         <v>414</v>
       </c>
-      <c r="C93" s="29"/>
-      <c r="D93" s="30"/>
-    </row>
-    <row r="94" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B94" s="31" t="s">
+      <c r="C93" s="37"/>
+      <c r="D93" s="38"/>
+    </row>
+    <row r="94" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B94" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="C94" s="31"/>
-      <c r="D94" s="31"/>
-    </row>
-    <row r="95" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="96" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="16" t="s">
+      <c r="C94" s="40"/>
+      <c r="D94" s="40"/>
+    </row>
+    <row r="95" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="96" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B96" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="C96" s="16"/>
-      <c r="D96" s="16"/>
-    </row>
-    <row r="97" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B97" s="28" t="s">
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+    </row>
+    <row r="97" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B97" s="36" t="s">
         <v>421</v>
       </c>
-      <c r="C97" s="29"/>
-      <c r="D97" s="30"/>
-    </row>
-    <row r="98" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B98" s="31" t="s">
+      <c r="C97" s="37"/>
+      <c r="D97" s="38"/>
+    </row>
+    <row r="98" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B98" s="40" t="s">
         <v>422</v>
       </c>
-      <c r="C98" s="31"/>
-      <c r="D98" s="31"/>
-    </row>
-    <row r="99" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="100" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B100" s="16" t="s">
+      <c r="C98" s="40"/>
+      <c r="D98" s="40"/>
+    </row>
+    <row r="99" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="100" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B100" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="C100" s="16"/>
-      <c r="D100" s="16"/>
-    </row>
-    <row r="101" spans="2:4" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B101" s="28" t="s">
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+    </row>
+    <row r="101" spans="2:4" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B101" s="36" t="s">
         <v>423</v>
       </c>
-      <c r="C101" s="29"/>
-      <c r="D101" s="30"/>
-    </row>
-    <row r="102" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="103" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B103" s="16" t="s">
+      <c r="C101" s="37"/>
+      <c r="D101" s="38"/>
+    </row>
+    <row r="102" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="103" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B103" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C103" s="16"/>
-      <c r="D103" s="16"/>
-    </row>
-    <row r="104" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B104" s="44" t="s">
+      <c r="C103" s="30"/>
+      <c r="D103" s="30"/>
+    </row>
+    <row r="104" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B104" s="26" t="s">
         <v>424</v>
       </c>
       <c r="C104" s="45" t="s">
@@ -17010,191 +14395,191 @@
       </c>
       <c r="D104" s="46"/>
     </row>
-    <row r="105" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B105" s="25" t="s">
+    <row r="105" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B105" s="21" t="s">
         <v>426</v>
       </c>
-      <c r="C105" s="40" t="s">
+      <c r="C105" s="47" t="s">
         <v>427</v>
       </c>
-      <c r="D105" s="47"/>
-    </row>
-    <row r="106" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B106" s="25" t="s">
+      <c r="D105" s="48"/>
+    </row>
+    <row r="106" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B106" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="C106" s="40" t="s">
+      <c r="C106" s="47" t="s">
         <v>429</v>
       </c>
-      <c r="D106" s="47"/>
-    </row>
-    <row r="107" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B107" s="23" t="s">
+      <c r="D106" s="48"/>
+    </row>
+    <row r="107" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B107" s="19" t="s">
         <v>430</v>
       </c>
-      <c r="C107" s="41" t="s">
+      <c r="C107" s="43" t="s">
         <v>431</v>
       </c>
-      <c r="D107" s="42"/>
-    </row>
-    <row r="108" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="109" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B109" s="16" t="s">
+      <c r="D107" s="44"/>
+    </row>
+    <row r="108" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="109" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B109" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="C109" s="16"/>
-      <c r="D109" s="16"/>
-    </row>
-    <row r="110" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B110" s="44" t="s">
+      <c r="C109" s="30"/>
+      <c r="D109" s="30"/>
+    </row>
+    <row r="110" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B110" s="26" t="s">
         <v>432</v>
       </c>
-      <c r="C110" s="43" t="s">
+      <c r="C110" s="25" t="s">
         <v>433</v>
       </c>
-      <c r="D110" s="48" t="s">
+      <c r="D110" s="27" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="111" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B111" s="25" t="s">
+    <row r="111" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B111" s="21" t="s">
         <v>435</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="15" t="s">
         <v>436</v>
       </c>
-      <c r="D111" s="26" t="s">
+      <c r="D111" s="22" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="112" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B112" s="25" t="s">
+    <row r="112" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B112" s="21" t="s">
         <v>438</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C112" s="15" t="s">
         <v>439</v>
       </c>
-      <c r="D112" s="26" t="s">
+      <c r="D112" s="22" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="113" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B113" s="25" t="s">
+    <row r="113" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B113" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" s="15" t="s">
         <v>442</v>
       </c>
-      <c r="D113" s="26" t="s">
+      <c r="D113" s="22" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="114" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B114" s="25" t="s">
+    <row r="114" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B114" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="C114" s="19" t="s">
+      <c r="C114" s="15" t="s">
         <v>445</v>
       </c>
-      <c r="D114" s="26" t="s">
+      <c r="D114" s="22" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="115" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B115" s="25" t="s">
+    <row r="115" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B115" s="21" t="s">
         <v>447</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="D115" s="26" t="s">
+      <c r="D115" s="22" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="116" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B116" s="25" t="s">
+    <row r="116" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B116" s="21" t="s">
         <v>450</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" s="15" t="s">
         <v>451</v>
       </c>
-      <c r="D116" s="26" t="s">
+      <c r="D116" s="22" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="117" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B117" s="23" t="s">
+    <row r="117" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B117" s="19" t="s">
         <v>453</v>
       </c>
-      <c r="C117" s="22" t="s">
+      <c r="C117" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="D117" s="24" t="s">
+      <c r="D117" s="20" t="s">
         <v>455</v>
       </c>
     </row>
-    <row r="118" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="119" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B119" s="16" t="s">
+    <row r="118" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="119" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B119" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="C119" s="16"/>
-      <c r="D119" s="16"/>
-    </row>
-    <row r="120" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B120" s="17" t="s">
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
+    </row>
+    <row r="120" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B120" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="C120" s="17"/>
-      <c r="D120" s="17"/>
-    </row>
-    <row r="121" spans="2:4" ht="180" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B121" s="17" t="s">
+      <c r="C120" s="31"/>
+      <c r="D120" s="31"/>
+    </row>
+    <row r="121" spans="2:4" ht="180" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B121" s="31" t="s">
         <v>456</v>
       </c>
-      <c r="C121" s="17"/>
-      <c r="D121" s="17"/>
-    </row>
-    <row r="122" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="123" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B123" s="16" t="s">
+      <c r="C121" s="31"/>
+      <c r="D121" s="31"/>
+    </row>
+    <row r="122" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="123" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B123" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C123" s="16"/>
-      <c r="D123" s="16"/>
-    </row>
-    <row r="124" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+    </row>
+    <row r="124" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B124" s="49" t="s">
         <v>457</v>
       </c>
       <c r="C124" s="49"/>
       <c r="D124" s="49"/>
     </row>
-    <row r="125" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B125" s="49" t="s">
         <v>458</v>
       </c>
       <c r="C125" s="49"/>
       <c r="D125" s="49"/>
     </row>
-    <row r="126" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="127" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="128" spans="2:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="127" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="128" spans="2:4" ht="33.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B128" s="50" t="s">
         <v>459</v>
       </c>
       <c r="C128" s="50"/>
       <c r="D128" s="50"/>
     </row>
-    <row r="129" spans="2:4" ht="18.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B129" s="15" t="s">
+    <row r="129" spans="2:4" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B129" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="C129" s="15"/>
-      <c r="D129" s="15"/>
-    </row>
-    <row r="130" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B130" s="44" t="s">
+      <c r="C129" s="29"/>
+      <c r="D129" s="29"/>
+    </row>
+    <row r="130" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B130" s="26" t="s">
         <v>424</v>
       </c>
       <c r="C130" s="45" t="s">
@@ -17202,311 +14587,311 @@
       </c>
       <c r="D130" s="46"/>
     </row>
-    <row r="131" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B131" s="25" t="s">
+    <row r="131" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B131" s="21" t="s">
         <v>461</v>
       </c>
-      <c r="C131" s="40" t="s">
+      <c r="C131" s="47" t="s">
         <v>462</v>
       </c>
-      <c r="D131" s="47"/>
-    </row>
-    <row r="132" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B132" s="25" t="s">
+      <c r="D131" s="48"/>
+    </row>
+    <row r="132" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B132" s="21" t="s">
         <v>463</v>
       </c>
-      <c r="C132" s="40" t="s">
+      <c r="C132" s="47" t="s">
         <v>464</v>
       </c>
-      <c r="D132" s="47"/>
-    </row>
-    <row r="133" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B133" s="23" t="s">
+      <c r="D132" s="48"/>
+    </row>
+    <row r="133" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B133" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="C133" s="41" t="s">
+      <c r="C133" s="43" t="s">
         <v>466</v>
       </c>
-      <c r="D133" s="42"/>
-    </row>
-    <row r="134" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="135" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B135" s="16" t="s">
+      <c r="D133" s="44"/>
+    </row>
+    <row r="134" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="135" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B135" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="C135" s="16"/>
-      <c r="D135" s="16"/>
-    </row>
-    <row r="136" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="28" t="s">
+      <c r="C135" s="30"/>
+      <c r="D135" s="30"/>
+    </row>
+    <row r="136" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B136" s="36" t="s">
         <v>467</v>
       </c>
-      <c r="C136" s="29"/>
-      <c r="D136" s="30"/>
-    </row>
-    <row r="137" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="138" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="16" t="s">
+      <c r="C136" s="37"/>
+      <c r="D136" s="38"/>
+    </row>
+    <row r="137" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="138" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B138" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="C138" s="16"/>
-      <c r="D138" s="16"/>
-    </row>
-    <row r="139" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B139" s="27" t="s">
+      <c r="C138" s="30"/>
+      <c r="D138" s="30"/>
+    </row>
+    <row r="139" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B139" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="27"/>
-      <c r="D139" s="27"/>
-    </row>
-    <row r="140" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B140" s="28" t="s">
+      <c r="C139" s="32"/>
+      <c r="D139" s="32"/>
+    </row>
+    <row r="140" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B140" s="36" t="s">
         <v>468</v>
       </c>
-      <c r="C140" s="29"/>
-      <c r="D140" s="30"/>
-    </row>
-    <row r="141" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B141" s="35" t="s">
+      <c r="C140" s="37"/>
+      <c r="D140" s="38"/>
+    </row>
+    <row r="141" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B141" s="39" t="s">
         <v>469</v>
       </c>
-      <c r="C141" s="35"/>
-      <c r="D141" s="35"/>
-    </row>
-    <row r="142" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B142" s="28" t="s">
+      <c r="C141" s="39"/>
+      <c r="D141" s="39"/>
+    </row>
+    <row r="142" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B142" s="36" t="s">
         <v>470</v>
       </c>
-      <c r="C142" s="29"/>
-      <c r="D142" s="30"/>
-    </row>
-    <row r="143" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B143" s="35" t="s">
+      <c r="C142" s="37"/>
+      <c r="D142" s="38"/>
+    </row>
+    <row r="143" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B143" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C143" s="35"/>
-      <c r="D143" s="35"/>
-    </row>
-    <row r="144" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B144" s="44" t="s">
+      <c r="C143" s="39"/>
+      <c r="D143" s="39"/>
+    </row>
+    <row r="144" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B144" s="26" t="s">
         <v>471</v>
       </c>
-      <c r="C144" s="43" t="s">
+      <c r="C144" s="25" t="s">
         <v>472</v>
       </c>
-      <c r="D144" s="48" t="s">
+      <c r="D144" s="27" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="145" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B145" s="25">
+    <row r="145" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B145" s="21">
         <v>20600</v>
       </c>
-      <c r="C145" s="19" t="b">
+      <c r="C145" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D145" s="26" t="s">
+      <c r="D145" s="22" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="146" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B146" s="25">
+    <row r="146" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B146" s="21">
         <v>20240</v>
       </c>
-      <c r="C146" s="19" t="b">
+      <c r="C146" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D146" s="26" t="s">
+      <c r="D146" s="22" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="147" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B147" s="25">
+    <row r="147" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B147" s="21">
         <v>20242</v>
       </c>
-      <c r="C147" s="19" t="b">
+      <c r="C147" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="D147" s="26" t="s">
+      <c r="D147" s="22" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="148" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B148" s="23" t="s">
+    <row r="148" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B148" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="C148" s="22" t="b">
+      <c r="C148" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="D148" s="24" t="s">
+      <c r="D148" s="20" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="149" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B149" s="31" t="s">
+    <row r="149" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B149" s="40" t="s">
         <v>477</v>
       </c>
-      <c r="C149" s="31"/>
-      <c r="D149" s="31"/>
-    </row>
-    <row r="150" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B150" s="27" t="s">
+      <c r="C149" s="40"/>
+      <c r="D149" s="40"/>
+    </row>
+    <row r="150" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B150" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="C150" s="27"/>
-      <c r="D150" s="27"/>
-    </row>
-    <row r="151" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B151" s="28" t="s">
+      <c r="C150" s="32"/>
+      <c r="D150" s="32"/>
+    </row>
+    <row r="151" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B151" s="36" t="s">
         <v>478</v>
       </c>
-      <c r="C151" s="29"/>
-      <c r="D151" s="30"/>
-    </row>
-    <row r="152" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B152" s="35" t="s">
+      <c r="C151" s="37"/>
+      <c r="D151" s="38"/>
+    </row>
+    <row r="152" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B152" s="39" t="s">
         <v>183</v>
       </c>
-      <c r="C152" s="35"/>
-      <c r="D152" s="35"/>
-    </row>
-    <row r="153" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B153" s="28" t="s">
+      <c r="C152" s="39"/>
+      <c r="D152" s="39"/>
+    </row>
+    <row r="153" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B153" s="36" t="s">
         <v>479</v>
       </c>
-      <c r="C153" s="29"/>
-      <c r="D153" s="30"/>
-    </row>
-    <row r="154" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="155" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B155" s="16" t="s">
+      <c r="C153" s="37"/>
+      <c r="D153" s="38"/>
+    </row>
+    <row r="154" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="155" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B155" s="30" t="s">
         <v>185</v>
       </c>
-      <c r="C155" s="16"/>
-      <c r="D155" s="16"/>
-    </row>
-    <row r="156" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B156" s="17" t="s">
+      <c r="C155" s="30"/>
+      <c r="D155" s="30"/>
+    </row>
+    <row r="156" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B156" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="C156" s="17"/>
-      <c r="D156" s="17"/>
-    </row>
-    <row r="157" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B157" s="27" t="s">
+      <c r="C156" s="31"/>
+      <c r="D156" s="31"/>
+    </row>
+    <row r="157" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B157" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="C157" s="27"/>
-      <c r="D157" s="27"/>
-    </row>
-    <row r="158" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B158" s="28" t="s">
+      <c r="C157" s="32"/>
+      <c r="D157" s="32"/>
+    </row>
+    <row r="158" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B158" s="36" t="s">
         <v>480</v>
       </c>
-      <c r="C158" s="29"/>
-      <c r="D158" s="30"/>
-    </row>
-    <row r="159" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B159" s="31" t="s">
+      <c r="C158" s="37"/>
+      <c r="D158" s="38"/>
+    </row>
+    <row r="159" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B159" s="40" t="s">
         <v>481</v>
       </c>
-      <c r="C159" s="31"/>
-      <c r="D159" s="31"/>
-    </row>
-    <row r="160" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B160" s="27" t="s">
+      <c r="C159" s="40"/>
+      <c r="D159" s="40"/>
+    </row>
+    <row r="160" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B160" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="C160" s="27"/>
-      <c r="D160" s="27"/>
-    </row>
-    <row r="161" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B161" s="28" t="s">
+      <c r="C160" s="32"/>
+      <c r="D160" s="32"/>
+    </row>
+    <row r="161" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B161" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="C161" s="29"/>
-      <c r="D161" s="30"/>
-    </row>
-    <row r="162" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B162" s="31" t="s">
+      <c r="C161" s="37"/>
+      <c r="D161" s="38"/>
+    </row>
+    <row r="162" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B162" s="40" t="s">
         <v>483</v>
       </c>
-      <c r="C162" s="31"/>
-      <c r="D162" s="31"/>
-    </row>
-    <row r="163" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B163" s="27" t="s">
+      <c r="C162" s="40"/>
+      <c r="D162" s="40"/>
+    </row>
+    <row r="163" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B163" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="C163" s="27"/>
-      <c r="D163" s="27"/>
-    </row>
-    <row r="164" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B164" s="28" t="s">
+      <c r="C163" s="32"/>
+      <c r="D163" s="32"/>
+    </row>
+    <row r="164" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B164" s="36" t="s">
         <v>484</v>
       </c>
-      <c r="C164" s="29"/>
-      <c r="D164" s="30"/>
-    </row>
-    <row r="165" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B165" s="31" t="s">
+      <c r="C164" s="37"/>
+      <c r="D164" s="38"/>
+    </row>
+    <row r="165" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B165" s="40" t="s">
         <v>485</v>
       </c>
-      <c r="C165" s="31"/>
-      <c r="D165" s="31"/>
-    </row>
-    <row r="166" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B166" s="27" t="s">
+      <c r="C165" s="40"/>
+      <c r="D165" s="40"/>
+    </row>
+    <row r="166" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B166" s="32" t="s">
         <v>198</v>
       </c>
-      <c r="C166" s="27"/>
-      <c r="D166" s="27"/>
-    </row>
-    <row r="167" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B167" s="17" t="s">
+      <c r="C166" s="32"/>
+      <c r="D166" s="32"/>
+    </row>
+    <row r="167" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B167" s="31" t="s">
         <v>486</v>
       </c>
-      <c r="C167" s="17"/>
-      <c r="D167" s="17"/>
-    </row>
-    <row r="168" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="169" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B169" s="16" t="s">
+      <c r="C167" s="31"/>
+      <c r="D167" s="31"/>
+    </row>
+    <row r="168" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="169" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B169" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="C169" s="16"/>
-      <c r="D169" s="16"/>
-    </row>
-    <row r="170" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B170" s="17" t="s">
+      <c r="C169" s="30"/>
+      <c r="D169" s="30"/>
+    </row>
+    <row r="170" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B170" s="31" t="s">
         <v>487</v>
       </c>
-      <c r="C170" s="17"/>
-      <c r="D170" s="17"/>
-    </row>
-    <row r="171" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B171" s="27" t="s">
+      <c r="C170" s="31"/>
+      <c r="D170" s="31"/>
+    </row>
+    <row r="171" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B171" s="32" t="s">
         <v>205</v>
       </c>
-      <c r="C171" s="27"/>
-      <c r="D171" s="27"/>
-    </row>
-    <row r="172" spans="2:4" ht="99.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B172" s="17" t="s">
+      <c r="C171" s="32"/>
+      <c r="D171" s="32"/>
+    </row>
+    <row r="172" spans="2:4" ht="99.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B172" s="31" t="s">
         <v>488</v>
       </c>
-      <c r="C172" s="17"/>
-      <c r="D172" s="17"/>
-    </row>
-    <row r="173" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B173" s="27" t="s">
+      <c r="C172" s="31"/>
+      <c r="D172" s="31"/>
+    </row>
+    <row r="173" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B173" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="C173" s="27"/>
-      <c r="D173" s="27"/>
-    </row>
-    <row r="174" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B174" s="44" t="s">
+      <c r="C173" s="32"/>
+      <c r="D173" s="32"/>
+    </row>
+    <row r="174" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B174" s="26" t="s">
         <v>489</v>
       </c>
       <c r="C174" s="45" t="s">
@@ -17514,189 +14899,189 @@
       </c>
       <c r="D174" s="46"/>
     </row>
-    <row r="175" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B175" s="25" t="s">
+    <row r="175" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B175" s="21" t="s">
         <v>491</v>
       </c>
-      <c r="C175" s="40" t="s">
+      <c r="C175" s="47" t="s">
         <v>492</v>
       </c>
-      <c r="D175" s="47"/>
-    </row>
-    <row r="176" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B176" s="25" t="s">
+      <c r="D175" s="48"/>
+    </row>
+    <row r="176" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B176" s="21" t="s">
         <v>414</v>
       </c>
-      <c r="C176" s="40" t="s">
+      <c r="C176" s="47" t="s">
         <v>493</v>
       </c>
-      <c r="D176" s="47"/>
-    </row>
-    <row r="177" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B177" s="25" t="s">
+      <c r="D176" s="48"/>
+    </row>
+    <row r="177" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B177" s="21" t="s">
         <v>494</v>
       </c>
-      <c r="C177" s="40" t="s">
+      <c r="C177" s="47" t="s">
         <v>495</v>
       </c>
-      <c r="D177" s="47"/>
-    </row>
-    <row r="178" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B178" s="25" t="s">
+      <c r="D177" s="48"/>
+    </row>
+    <row r="178" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B178" s="21" t="s">
         <v>365</v>
       </c>
-      <c r="C178" s="40" t="s">
+      <c r="C178" s="47" t="s">
         <v>496</v>
       </c>
-      <c r="D178" s="47"/>
-    </row>
-    <row r="179" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B179" s="23" t="s">
+      <c r="D178" s="48"/>
+    </row>
+    <row r="179" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B179" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="C179" s="41" t="s">
+      <c r="C179" s="43" t="s">
         <v>497</v>
       </c>
-      <c r="D179" s="42"/>
-    </row>
-    <row r="180" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B180" s="35" t="s">
+      <c r="D179" s="44"/>
+    </row>
+    <row r="180" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B180" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="C180" s="35"/>
-      <c r="D180" s="35"/>
-    </row>
-    <row r="181" spans="2:4" ht="51.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B181" s="17" t="s">
+      <c r="C180" s="39"/>
+      <c r="D180" s="39"/>
+    </row>
+    <row r="181" spans="2:4" ht="51.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B181" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="C181" s="17"/>
-      <c r="D181" s="17"/>
-    </row>
-    <row r="182" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B182" s="17" t="s">
+      <c r="C181" s="31"/>
+      <c r="D181" s="31"/>
+    </row>
+    <row r="182" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B182" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="C182" s="17"/>
-      <c r="D182" s="17"/>
-    </row>
-    <row r="183" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="184" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B184" s="16" t="s">
+      <c r="C182" s="31"/>
+      <c r="D182" s="31"/>
+    </row>
+    <row r="183" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="184" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B184" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="C184" s="16"/>
-      <c r="D184" s="16"/>
-    </row>
-    <row r="185" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B185" s="27" t="s">
+      <c r="C184" s="30"/>
+      <c r="D184" s="30"/>
+    </row>
+    <row r="185" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B185" s="32" t="s">
         <v>500</v>
       </c>
-      <c r="C185" s="27"/>
-      <c r="D185" s="27"/>
-    </row>
-    <row r="186" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B186" s="28" t="s">
+      <c r="C185" s="32"/>
+      <c r="D185" s="32"/>
+    </row>
+    <row r="186" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B186" s="36" t="s">
         <v>501</v>
       </c>
-      <c r="C186" s="29"/>
-      <c r="D186" s="30"/>
-    </row>
-    <row r="187" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B187" s="35" t="s">
+      <c r="C186" s="37"/>
+      <c r="D186" s="38"/>
+    </row>
+    <row r="187" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B187" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="C187" s="35"/>
-      <c r="D187" s="35"/>
-    </row>
-    <row r="188" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B188" s="28" t="s">
+      <c r="C187" s="39"/>
+      <c r="D187" s="39"/>
+    </row>
+    <row r="188" spans="2:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B188" s="36" t="s">
         <v>502</v>
       </c>
-      <c r="C188" s="29"/>
-      <c r="D188" s="30"/>
-    </row>
-    <row r="189" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B189" s="35" t="s">
+      <c r="C188" s="37"/>
+      <c r="D188" s="38"/>
+    </row>
+    <row r="189" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B189" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C189" s="35"/>
-      <c r="D189" s="35"/>
-    </row>
-    <row r="190" spans="2:4" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B190" s="28" t="s">
+      <c r="C189" s="39"/>
+      <c r="D189" s="39"/>
+    </row>
+    <row r="190" spans="2:4" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B190" s="36" t="s">
         <v>503</v>
       </c>
-      <c r="C190" s="29"/>
-      <c r="D190" s="30"/>
-    </row>
-    <row r="191" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B191" s="31" t="s">
+      <c r="C190" s="37"/>
+      <c r="D190" s="38"/>
+    </row>
+    <row r="191" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B191" s="40" t="s">
         <v>504</v>
       </c>
-      <c r="C191" s="31"/>
-      <c r="D191" s="31"/>
-    </row>
-    <row r="192" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B192" s="17" t="s">
+      <c r="C191" s="40"/>
+      <c r="D191" s="40"/>
+    </row>
+    <row r="192" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B192" s="31" t="s">
         <v>505</v>
       </c>
-      <c r="C192" s="17"/>
-      <c r="D192" s="17"/>
-    </row>
-    <row r="193" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="194" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B194" s="16" t="s">
+      <c r="C192" s="31"/>
+      <c r="D192" s="31"/>
+    </row>
+    <row r="193" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="194" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B194" s="30" t="s">
         <v>506</v>
       </c>
-      <c r="C194" s="16"/>
-      <c r="D194" s="16"/>
-    </row>
-    <row r="195" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B195" s="17" t="s">
+      <c r="C194" s="30"/>
+      <c r="D194" s="30"/>
+    </row>
+    <row r="195" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B195" s="31" t="s">
         <v>507</v>
       </c>
-      <c r="C195" s="17"/>
-      <c r="D195" s="17"/>
-    </row>
-    <row r="196" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B196" s="27" t="s">
+      <c r="C195" s="31"/>
+      <c r="D195" s="31"/>
+    </row>
+    <row r="196" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B196" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="C196" s="27"/>
-      <c r="D196" s="27"/>
-    </row>
-    <row r="197" spans="2:4" ht="51.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B197" s="17" t="s">
+      <c r="C196" s="32"/>
+      <c r="D196" s="32"/>
+    </row>
+    <row r="197" spans="2:4" ht="51.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B197" s="31" t="s">
         <v>508</v>
       </c>
-      <c r="C197" s="17"/>
-      <c r="D197" s="17"/>
-    </row>
-    <row r="198" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B198" s="27" t="s">
+      <c r="C197" s="31"/>
+      <c r="D197" s="31"/>
+    </row>
+    <row r="198" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B198" s="32" t="s">
         <v>247</v>
       </c>
-      <c r="C198" s="27"/>
-      <c r="D198" s="27"/>
-    </row>
-    <row r="199" spans="2:4" ht="84" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B199" s="17" t="s">
+      <c r="C198" s="32"/>
+      <c r="D198" s="32"/>
+    </row>
+    <row r="199" spans="2:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B199" s="31" t="s">
         <v>509</v>
       </c>
-      <c r="C199" s="17"/>
-      <c r="D199" s="17"/>
-    </row>
-    <row r="200" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="201" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B201" s="16" t="s">
+      <c r="C199" s="31"/>
+      <c r="D199" s="31"/>
+    </row>
+    <row r="200" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="201" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B201" s="30" t="s">
         <v>253</v>
       </c>
-      <c r="C201" s="16"/>
-      <c r="D201" s="16"/>
-    </row>
-    <row r="202" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B202" s="44" t="s">
+      <c r="C201" s="30"/>
+      <c r="D201" s="30"/>
+    </row>
+    <row r="202" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B202" s="26" t="s">
         <v>510</v>
       </c>
       <c r="C202" s="45" t="s">
@@ -17704,160 +15089,160 @@
       </c>
       <c r="D202" s="46"/>
     </row>
-    <row r="203" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B203" s="25" t="s">
+    <row r="203" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B203" s="21" t="s">
         <v>511</v>
       </c>
-      <c r="C203" s="40" t="s">
+      <c r="C203" s="47" t="s">
         <v>512</v>
       </c>
-      <c r="D203" s="47"/>
-    </row>
-    <row r="204" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B204" s="25" t="s">
+      <c r="D203" s="48"/>
+    </row>
+    <row r="204" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B204" s="21" t="s">
         <v>513</v>
       </c>
-      <c r="C204" s="40" t="s">
+      <c r="C204" s="47" t="s">
         <v>512</v>
       </c>
-      <c r="D204" s="47"/>
-    </row>
-    <row r="205" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B205" s="25" t="s">
+      <c r="D204" s="48"/>
+    </row>
+    <row r="205" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B205" s="21" t="s">
         <v>514</v>
       </c>
-      <c r="C205" s="40" t="s">
+      <c r="C205" s="47" t="s">
         <v>512</v>
       </c>
-      <c r="D205" s="47"/>
-    </row>
-    <row r="206" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B206" s="25" t="s">
+      <c r="D205" s="48"/>
+    </row>
+    <row r="206" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B206" s="21" t="s">
         <v>515</v>
       </c>
-      <c r="C206" s="40" t="s">
+      <c r="C206" s="47" t="s">
         <v>512</v>
       </c>
-      <c r="D206" s="47"/>
-    </row>
-    <row r="207" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B207" s="25" t="s">
+      <c r="D206" s="48"/>
+    </row>
+    <row r="207" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B207" s="21" t="s">
         <v>516</v>
       </c>
-      <c r="C207" s="40" t="s">
+      <c r="C207" s="47" t="s">
         <v>512</v>
       </c>
-      <c r="D207" s="47"/>
-    </row>
-    <row r="208" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B208" s="23" t="s">
+      <c r="D207" s="48"/>
+    </row>
+    <row r="208" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B208" s="19" t="s">
         <v>517</v>
       </c>
-      <c r="C208" s="41" t="s">
+      <c r="C208" s="43" t="s">
         <v>518</v>
       </c>
-      <c r="D208" s="42"/>
-    </row>
-    <row r="209" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B209" s="31" t="s">
+      <c r="D208" s="44"/>
+    </row>
+    <row r="209" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B209" s="40" t="s">
         <v>519</v>
       </c>
-      <c r="C209" s="31"/>
-      <c r="D209" s="31"/>
-    </row>
-    <row r="210" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="211" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B211" s="16" t="s">
+      <c r="C209" s="40"/>
+      <c r="D209" s="40"/>
+    </row>
+    <row r="210" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="211" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B211" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="C211" s="16"/>
-      <c r="D211" s="16"/>
-    </row>
-    <row r="212" spans="2:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B212" s="44" t="s">
+      <c r="C211" s="30"/>
+      <c r="D211" s="30"/>
+    </row>
+    <row r="212" spans="2:4" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B212" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="C212" s="43" t="s">
+      <c r="C212" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="D212" s="48" t="s">
+      <c r="D212" s="27" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="213" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B213" s="25" t="s">
+    <row r="213" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B213" s="21" t="s">
         <v>522</v>
       </c>
-      <c r="C213" s="19" t="s">
+      <c r="C213" s="15" t="s">
         <v>523</v>
       </c>
-      <c r="D213" s="26" t="s">
+      <c r="D213" s="22" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="214" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B214" s="25" t="s">
+    <row r="214" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B214" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="C214" s="19" t="s">
+      <c r="C214" s="15" t="s">
         <v>526</v>
       </c>
-      <c r="D214" s="26" t="s">
+      <c r="D214" s="22" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="215" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B215" s="25" t="s">
+    <row r="215" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B215" s="21" t="s">
         <v>528</v>
       </c>
-      <c r="C215" s="19" t="s">
+      <c r="C215" s="15" t="s">
         <v>529</v>
       </c>
-      <c r="D215" s="26" t="s">
+      <c r="D215" s="22" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="216" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B216" s="23" t="s">
+    <row r="216" spans="2:4" ht="38.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B216" s="19" t="s">
         <v>531</v>
       </c>
-      <c r="C216" s="22" t="s">
+      <c r="C216" s="18" t="s">
         <v>532</v>
       </c>
-      <c r="D216" s="24" t="s">
+      <c r="D216" s="20" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="217" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="218" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B218" s="16" t="s">
+    <row r="217" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="218" spans="2:4" ht="26.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B218" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C218" s="16"/>
-      <c r="D218" s="16"/>
-    </row>
-    <row r="219" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C218" s="30"/>
+      <c r="D218" s="30"/>
+    </row>
+    <row r="219" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B219" s="49" t="s">
         <v>534</v>
       </c>
       <c r="C219" s="49"/>
       <c r="D219" s="49"/>
     </row>
-    <row r="220" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="2:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B220" s="49" t="s">
         <v>276</v>
       </c>
       <c r="C220" s="49"/>
       <c r="D220" s="49"/>
     </row>
-    <row r="221" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B221" s="49" t="s">
         <v>535</v>
       </c>
       <c r="C221" s="49"/>
       <c r="D221" s="49"/>
     </row>
-    <row r="222" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="222" spans="2:4" ht="8.1" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <mergeCells count="171">
     <mergeCell ref="B211:D211"/>
@@ -17955,9 +15340,6 @@
     <mergeCell ref="B96:D96"/>
     <mergeCell ref="B97:D97"/>
     <mergeCell ref="B98:D98"/>
-    <mergeCell ref="B86:D86"/>
-    <mergeCell ref="B87:D87"/>
-    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B89:D89"/>
     <mergeCell ref="B90:D90"/>
     <mergeCell ref="B91:D91"/>
@@ -17967,11 +15349,15 @@
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="B84:D84"/>
     <mergeCell ref="B85:D85"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="B54:D54"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B87:D87"/>
+    <mergeCell ref="B88:D88"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B71:D71"/>
     <mergeCell ref="B72:D72"/>
@@ -17985,12 +15371,6 @@
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B54:D54"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="B49:D49"/>
     <mergeCell ref="B50:D50"/>
@@ -18013,9 +15393,11 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B24:D24"/>
@@ -18031,19 +15413,2637 @@
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <phoneticPr fontId="12"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34456845-7BEB-47A3-AFC6-90E43EAB56EA}">
+  <dimension ref="A1:B78"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="2" max="2" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="26.1" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:2" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="1"/>
+      <c r="B4" s="9" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="1"/>
+      <c r="B5" s="9" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="1"/>
+      <c r="B6" s="9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="1"/>
+      <c r="B7" s="9" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="1"/>
+      <c r="B8" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="1"/>
+      <c r="B9" s="9" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:2" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="1"/>
+      <c r="B11" s="7" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="1"/>
+      <c r="B12" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="1"/>
+      <c r="B14" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="1"/>
+      <c r="B15" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="1"/>
+      <c r="B16" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="1"/>
+      <c r="B17" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="1"/>
+      <c r="B18" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="1"/>
+      <c r="B19" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1"/>
+      <c r="B22" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1"/>
+      <c r="B23" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="1"/>
+      <c r="B24" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="1"/>
+      <c r="B25" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="1"/>
+      <c r="B26" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="1"/>
+      <c r="B27" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="1"/>
+      <c r="B30" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="1"/>
+      <c r="B31" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="1"/>
+      <c r="B32" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="1"/>
+      <c r="B33" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="1"/>
+      <c r="B34" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="1"/>
+      <c r="B35" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+    </row>
+    <row r="37" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+    </row>
+    <row r="38" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="1"/>
+      <c r="B38" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="1"/>
+      <c r="B39" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="1"/>
+      <c r="B40" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="1"/>
+      <c r="B41" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="1"/>
+      <c r="B42" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="1"/>
+      <c r="B43" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+    </row>
+    <row r="45" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+    </row>
+    <row r="46" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="1"/>
+      <c r="B46" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="1"/>
+      <c r="B47" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="1"/>
+      <c r="B48" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="1"/>
+      <c r="B49" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="1"/>
+      <c r="B50" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="1"/>
+      <c r="B51" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="1"/>
+      <c r="B54" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="1"/>
+      <c r="B55" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="1"/>
+      <c r="B56" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="1"/>
+      <c r="B57" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="57.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="1"/>
+      <c r="B58" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="1"/>
+      <c r="B59" s="8" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="345" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="1:2" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+    </row>
+    <row r="63" spans="1:2" ht="21.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="1"/>
+      <c r="B63" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="1"/>
+      <c r="B64" s="10" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="1"/>
+      <c r="B65" s="10" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="1"/>
+      <c r="B66" s="10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="1"/>
+      <c r="B67" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="1"/>
+      <c r="B68" s="10"/>
+    </row>
+    <row r="69" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="1"/>
+      <c r="B69" s="10" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="1"/>
+      <c r="B70" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="1"/>
+      <c r="B71" s="10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="1"/>
+      <c r="B72" s="10"/>
+    </row>
+    <row r="73" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="1"/>
+      <c r="B73" s="10" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A74" s="1"/>
+      <c r="B74" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A75" s="1"/>
+      <c r="B75" s="10"/>
+    </row>
+    <row r="76" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A76" s="1"/>
+      <c r="B76" s="10" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="8.1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A77" s="1"/>
+      <c r="B77" s="10"/>
+    </row>
+    <row r="78" spans="1:2" ht="15.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A78" s="1"/>
+      <c r="B78" s="10" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{764764F8-C3DF-4CCD-BFFC-91EDD895FCA3}">
+  <dimension ref="B1:H21"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.3984375" customWidth="1"/>
+    <col min="2" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" ht="26.4" x14ac:dyDescent="0.65">
+      <c r="B1" s="11" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B3" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B4" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B6" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>330</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B7" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="13">
+        <v>5</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B8" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="E8" s="13">
+        <v>8</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E9" s="13">
+        <v>5</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E10" s="13">
+        <v>5</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B11" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E11" s="13">
+        <v>5</v>
+      </c>
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B12" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="E12" s="13">
+        <v>5</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B13" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="13">
+        <v>5</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E14" s="13">
+        <v>5</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E15" s="13">
+        <v>5</v>
+      </c>
+      <c r="F15" s="13">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B16" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E16" s="13">
+        <v>5</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0</v>
+      </c>
+      <c r="G16" s="13">
+        <v>0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B17" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E17" s="13">
+        <v>5</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0</v>
+      </c>
+      <c r="G17" s="13">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B18" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="E18" s="13">
+        <v>5</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0</v>
+      </c>
+      <c r="H18" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B19" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E19" s="13">
+        <v>5</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0</v>
+      </c>
+      <c r="G19" s="13">
+        <v>1</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B20" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E20" s="13">
+        <v>5</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0</v>
+      </c>
+      <c r="G20" s="13">
+        <v>0</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B21" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>335</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E21" s="13">
+        <v>5</v>
+      </c>
+      <c r="F21" s="13">
+        <v>0</v>
+      </c>
+      <c r="G21" s="13">
+        <v>1</v>
+      </c>
+      <c r="H21" s="13">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5BDDF42-8BF6-470F-AACD-219DA18F494C}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB633387-CCD0-4B36-A8AF-1DE88DA1214B}">
+  <dimension ref="D86:D88"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D86" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.45">
+      <c r="D88" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF4739C-E82B-4160-8B82-56A8AC8BED06}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <phoneticPr fontId="12"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <customProperties>
+    <customPr name="CafeStyleVersion" r:id="rId1"/>
+  </customProperties>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1291689E-9DDA-4BB4-AB16-F66FF3387759}">
+  <dimension ref="B2:B281"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B71" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B87" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B91" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B94" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B99" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B101" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B103" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B104" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B105" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B107" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B108" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B109" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B111" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B115" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B118" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B119" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="121" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B121" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B123" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B124" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B126" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="127" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B127" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B128" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B129" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B130" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B132" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B133" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B134" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B135" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B136" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B138" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B139" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B140" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B142" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B143" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B144" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B145" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B146" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B147" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B149" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B150" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B151" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B153" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B154" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B157" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B158" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B161" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B163" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="165" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B165" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B167" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B168" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B171" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B172" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B173" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B175" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B176" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B178" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B179" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B181" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B182" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B183" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="185" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B185" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B186" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B188" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B190" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B191" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B193" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B194" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B196" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B197" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B198" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="201" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B201" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B202" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B203" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B205" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B207" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B208" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B209" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B212" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="213" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B213" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B214" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B216" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B217" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B218" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B219" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B222" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B223" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B224" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B226" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B227" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B228" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B231" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B232" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B233" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B235" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B236" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B237" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B238" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B239" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B240" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="241" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B241" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="242" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B242" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="243" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B243" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="245" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B245" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="246" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B246" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="247" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B247" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="248" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B248" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="251" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B251" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="252" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B252" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="253" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B253" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="255" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B255" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="257" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B257" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B258" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="259" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B259" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="260" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B260" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="261" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B261" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="262" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B262" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="263" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B263" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="264" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B264" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="265" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B265" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="266" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B266" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="267" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B267" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="270" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B270" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B271" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="272" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B272" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B274" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="275" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B275" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B277" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="278" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B278" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="279" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B279" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B281" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70691334-4224-4996-88DA-06244D2EDD3B}">
+  <dimension ref="B2:B198"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="13" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B73" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B74" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B77" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B78" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B80" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B81" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B82" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B83" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B84" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B85" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B86" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B88" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B89" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B90" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="91" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B91" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B92" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B95" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B96" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B97" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B98" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B100" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B101" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B102" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B103" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B107" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B110" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B111" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="113" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B113" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="114" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B114" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="116" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B116" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="117" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B117" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="118" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B118" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="119" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B119" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="120" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B120" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="122" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B122" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="123" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B123" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="124" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B124" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="126" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B126" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B129" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B130" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B131" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B133" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B134" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B135" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B137" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="138" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B138" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="139" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B139" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="140" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B140" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="142" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B142" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="143" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B143" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="144" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B144" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B145" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B146" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B147" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B151" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B154" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="155" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B155" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B156" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B157" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B158" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="159" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B159" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B160" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="161" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B161" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="163" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B163" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="166" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B167" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="168" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B168" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B170" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="171" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B171" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="172" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B172" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="173" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B173" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="175" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B175" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="176" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B176" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B178" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B179" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="181" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B181" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="182" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B182" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="183" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B183" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="186" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B186" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B187" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="188" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B188" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B190" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="191" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B191" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B193" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B195" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B196" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.45">
+      <c r="B198" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>